--- a/runtime/apps/wechat_ai_customer_service/test_artifacts/workflow_logic_customer_leads.xlsx
+++ b/runtime/apps/wechat_ai_customer_service/test_artifacts/workflow_logic_customer_leads.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06T02:46:08</t>
+          <t>2026-05-10T16:16:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/runtime/apps/wechat_ai_customer_service/test_artifacts/workflow_logic_customer_leads.xlsx
+++ b/runtime/apps/wechat_ai_customer_service/test_artifacts/workflow_logic_customer_leads.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-10T16:16:38</t>
+          <t>2026-05-19T13:30:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
